--- a/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
